--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ163"/>
+  <dimension ref="A1:AZ172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6193,48 +6193,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111061812</v>
+        <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>91872</v>
+        <v>93426</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485828</v>
+        <v>485898</v>
       </c>
       <c r="R54" t="n">
-        <v>6917531</v>
+        <v>6917755</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6258,12 +6258,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 mycel</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6278,69 +6293,74 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061812</t>
+          <t>https://artportalen.se/Sighting/137163134</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111060619</v>
+        <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>93426</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485725</v>
+        <v>485916</v>
       </c>
       <c r="R55" t="n">
-        <v>6917358</v>
+        <v>6917596</v>
       </c>
       <c r="S55" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6364,12 +6384,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6384,69 +6414,74 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060619</t>
+          <t>https://artportalen.se/Sighting/137163135</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111062486</v>
+        <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>93426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485721</v>
+        <v>485940</v>
       </c>
       <c r="R56" t="n">
-        <v>6917334</v>
+        <v>6917543</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6470,12 +6505,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6490,69 +6535,74 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062486</t>
+          <t>https://artportalen.se/Sighting/137163136</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111062793</v>
+        <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>79327</v>
+        <v>93426</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485708</v>
+        <v>485932</v>
       </c>
       <c r="R57" t="n">
-        <v>6917329</v>
+        <v>6917578</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6576,12 +6626,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6596,69 +6656,74 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062793</t>
+          <t>https://artportalen.se/Sighting/137163137</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>111062794</v>
+        <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>93426</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485664</v>
+        <v>485750</v>
       </c>
       <c r="R58" t="n">
-        <v>6917230</v>
+        <v>6917215</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6682,12 +6747,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6702,31 +6777,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062794</t>
+          <t>https://artportalen.se/Sighting/137163139</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>111060695</v>
+        <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>78730</v>
+        <v>93426</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6734,37 +6805,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485595</v>
+        <v>485680</v>
       </c>
       <c r="R59" t="n">
-        <v>6917191</v>
+        <v>6917267</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6788,12 +6868,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6808,66 +6898,62 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060695</t>
+          <t>https://artportalen.se/Sighting/137163140</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>111062806</v>
+        <v>111061812</v>
       </c>
       <c r="B60" t="n">
-        <v>78730</v>
+        <v>91872</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485576</v>
+        <v>485828</v>
       </c>
       <c r="R60" t="n">
-        <v>6917155</v>
+        <v>6917531</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6914,12 +7000,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6929,38 +7015,38 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062806</t>
+          <t>https://artportalen.se/Sighting/111061812</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>111062807</v>
+        <v>111060619</v>
       </c>
       <c r="B61" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6970,13 +7056,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485610</v>
+        <v>485725</v>
       </c>
       <c r="R61" t="n">
-        <v>6917147</v>
+        <v>6917358</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7020,12 +7106,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7035,38 +7121,38 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062807</t>
+          <t>https://artportalen.se/Sighting/111060619</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>111062808</v>
+        <v>111062486</v>
       </c>
       <c r="B62" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7076,10 +7162,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>485610</v>
+        <v>485721</v>
       </c>
       <c r="R62" t="n">
-        <v>6917163</v>
+        <v>6917334</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7126,12 +7212,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7141,54 +7227,54 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062808</t>
+          <t>https://artportalen.se/Sighting/111062486</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>91845857</v>
+        <v>111062793</v>
       </c>
       <c r="B63" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485599</v>
+        <v>485708</v>
       </c>
       <c r="R63" t="n">
-        <v>6917016</v>
+        <v>6917329</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7212,12 +7298,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7232,69 +7318,69 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91845857</t>
+          <t>https://artportalen.se/Sighting/111062793</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>91846013</v>
+        <v>111062794</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485620</v>
+        <v>485664</v>
       </c>
       <c r="R64" t="n">
-        <v>6917095</v>
+        <v>6917230</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7318,12 +7404,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7338,31 +7424,31 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91846013</t>
+          <t>https://artportalen.se/Sighting/111062794</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>111060615</v>
+        <v>111060695</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7370,21 +7456,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7394,13 +7480,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485805</v>
+        <v>485595</v>
       </c>
       <c r="R65" t="n">
-        <v>6917416</v>
+        <v>6917191</v>
       </c>
       <c r="S65" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7444,12 +7530,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7459,16 +7545,16 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060615</t>
+          <t>https://artportalen.se/Sighting/111060695</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>111060616</v>
+        <v>111062806</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7476,21 +7562,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7500,13 +7586,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485793</v>
+        <v>485576</v>
       </c>
       <c r="R66" t="n">
-        <v>6917210</v>
+        <v>6917155</v>
       </c>
       <c r="S66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7550,12 +7636,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7565,16 +7651,16 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060616</t>
+          <t>https://artportalen.se/Sighting/111062806</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>111060617</v>
+        <v>111062807</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,21 +7668,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7606,13 +7692,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>485674</v>
+        <v>485610</v>
       </c>
       <c r="R67" t="n">
-        <v>6917036</v>
+        <v>6917147</v>
       </c>
       <c r="S67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7656,12 +7742,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7671,16 +7757,16 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060617</t>
+          <t>https://artportalen.se/Sighting/111062807</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>111060618</v>
+        <v>111062808</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7688,21 +7774,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7712,13 +7798,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>485602</v>
+        <v>485610</v>
       </c>
       <c r="R68" t="n">
-        <v>6916978</v>
+        <v>6917163</v>
       </c>
       <c r="S68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7762,12 +7848,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7777,13 +7863,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060618</t>
+          <t>https://artportalen.se/Sighting/111062808</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>111061828</v>
+        <v>91845857</v>
       </c>
       <c r="B69" t="n">
         <v>79084</v>
@@ -7814,17 +7900,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>485796</v>
+        <v>485599</v>
       </c>
       <c r="R69" t="n">
-        <v>6917431</v>
+        <v>6917016</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7848,12 +7934,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7868,28 +7954,28 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061828</t>
+          <t>https://artportalen.se/Sighting/91845857</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>111061829</v>
+        <v>91846013</v>
       </c>
       <c r="B70" t="n">
         <v>79084</v>
@@ -7920,17 +8006,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>485626</v>
+        <v>485620</v>
       </c>
       <c r="R70" t="n">
-        <v>6917100</v>
+        <v>6917095</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7954,12 +8040,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7974,28 +8060,28 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061829</t>
+          <t>https://artportalen.se/Sighting/91846013</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>111062479</v>
+        <v>111060615</v>
       </c>
       <c r="B71" t="n">
         <v>79084</v>
@@ -8030,13 +8116,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485593</v>
+        <v>485805</v>
       </c>
       <c r="R71" t="n">
-        <v>6916962</v>
+        <v>6917416</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8080,12 +8166,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8095,13 +8181,13 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062479</t>
+          <t>https://artportalen.se/Sighting/111060615</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>111062480</v>
+        <v>111060616</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -8136,13 +8222,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485599</v>
+        <v>485793</v>
       </c>
       <c r="R72" t="n">
-        <v>6916956</v>
+        <v>6917210</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8186,12 +8272,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8201,13 +8287,13 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062480</t>
+          <t>https://artportalen.se/Sighting/111060616</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>111062481</v>
+        <v>111060617</v>
       </c>
       <c r="B73" t="n">
         <v>79084</v>
@@ -8242,13 +8328,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485586</v>
+        <v>485674</v>
       </c>
       <c r="R73" t="n">
-        <v>6916954</v>
+        <v>6917036</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8292,12 +8378,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8307,13 +8393,13 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062481</t>
+          <t>https://artportalen.se/Sighting/111060617</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>111062776</v>
+        <v>111060618</v>
       </c>
       <c r="B74" t="n">
         <v>79084</v>
@@ -8348,13 +8434,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>485799</v>
+        <v>485602</v>
       </c>
       <c r="R74" t="n">
-        <v>6917549</v>
+        <v>6916978</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8398,12 +8484,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8413,13 +8499,13 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062776</t>
+          <t>https://artportalen.se/Sighting/111060618</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>111062777</v>
+        <v>111061828</v>
       </c>
       <c r="B75" t="n">
         <v>79084</v>
@@ -8450,14 +8536,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>485801</v>
+        <v>485796</v>
       </c>
       <c r="R75" t="n">
-        <v>6917380</v>
+        <v>6917431</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8504,12 +8590,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8519,13 +8605,13 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062777</t>
+          <t>https://artportalen.se/Sighting/111061828</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>111062778</v>
+        <v>111061829</v>
       </c>
       <c r="B76" t="n">
         <v>79084</v>
@@ -8556,14 +8642,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>485624</v>
+        <v>485626</v>
       </c>
       <c r="R76" t="n">
-        <v>6917099</v>
+        <v>6917100</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8610,12 +8696,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8625,13 +8711,13 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062778</t>
+          <t>https://artportalen.se/Sighting/111061829</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>111062779</v>
+        <v>111062479</v>
       </c>
       <c r="B77" t="n">
         <v>79084</v>
@@ -8666,10 +8752,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485608</v>
+        <v>485593</v>
       </c>
       <c r="R77" t="n">
-        <v>6917019</v>
+        <v>6916962</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8716,12 +8802,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8731,13 +8817,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062779</t>
+          <t>https://artportalen.se/Sighting/111062479</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>111062780</v>
+        <v>111062480</v>
       </c>
       <c r="B78" t="n">
         <v>79084</v>
@@ -8772,10 +8858,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485597</v>
+        <v>485599</v>
       </c>
       <c r="R78" t="n">
-        <v>6917003</v>
+        <v>6916956</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -8822,12 +8908,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8837,13 +8923,13 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062780</t>
+          <t>https://artportalen.se/Sighting/111062480</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>111062781</v>
+        <v>111062481</v>
       </c>
       <c r="B79" t="n">
         <v>79084</v>
@@ -8878,10 +8964,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>485606</v>
+        <v>485586</v>
       </c>
       <c r="R79" t="n">
-        <v>6916994</v>
+        <v>6916954</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8928,12 +9014,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8943,13 +9029,13 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062781</t>
+          <t>https://artportalen.se/Sighting/111062481</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>111062782</v>
+        <v>111062776</v>
       </c>
       <c r="B80" t="n">
         <v>79084</v>
@@ -8984,10 +9070,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>485614</v>
+        <v>485799</v>
       </c>
       <c r="R80" t="n">
-        <v>6916959</v>
+        <v>6917549</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9049,13 +9135,13 @@
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062782</t>
+          <t>https://artportalen.se/Sighting/111062776</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>111062783</v>
+        <v>111062777</v>
       </c>
       <c r="B81" t="n">
         <v>79084</v>
@@ -9090,10 +9176,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>485601</v>
+        <v>485801</v>
       </c>
       <c r="R81" t="n">
-        <v>6916956</v>
+        <v>6917380</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9155,13 +9241,13 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062783</t>
+          <t>https://artportalen.se/Sighting/111062777</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>111063031</v>
+        <v>111062778</v>
       </c>
       <c r="B82" t="n">
         <v>79084</v>
@@ -9192,14 +9278,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>485601</v>
+        <v>485624</v>
       </c>
       <c r="R82" t="n">
-        <v>6917014</v>
+        <v>6917099</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9246,12 +9332,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9261,13 +9347,13 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111063031</t>
+          <t>https://artportalen.se/Sighting/111062778</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>111064863</v>
+        <v>111062779</v>
       </c>
       <c r="B83" t="n">
         <v>79084</v>
@@ -9298,14 +9384,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>485715</v>
+        <v>485608</v>
       </c>
       <c r="R83" t="n">
-        <v>6917095</v>
+        <v>6917019</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9352,12 +9438,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9367,13 +9453,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064863</t>
+          <t>https://artportalen.se/Sighting/111062779</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>111064864</v>
+        <v>111062780</v>
       </c>
       <c r="B84" t="n">
         <v>79084</v>
@@ -9404,14 +9490,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>485628</v>
+        <v>485597</v>
       </c>
       <c r="R84" t="n">
-        <v>6916956</v>
+        <v>6917003</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9458,12 +9544,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9473,13 +9559,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064864</t>
+          <t>https://artportalen.se/Sighting/111062780</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>111064865</v>
+        <v>111062781</v>
       </c>
       <c r="B85" t="n">
         <v>79084</v>
@@ -9510,14 +9596,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>485894</v>
+        <v>485606</v>
       </c>
       <c r="R85" t="n">
-        <v>6917512</v>
+        <v>6916994</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9564,12 +9650,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9579,13 +9665,13 @@
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064865</t>
+          <t>https://artportalen.se/Sighting/111062781</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>111064866</v>
+        <v>111062782</v>
       </c>
       <c r="B86" t="n">
         <v>79084</v>
@@ -9616,14 +9702,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>485612</v>
+        <v>485614</v>
       </c>
       <c r="R86" t="n">
-        <v>6917029</v>
+        <v>6916959</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9670,12 +9756,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9685,13 +9771,13 @@
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064866</t>
+          <t>https://artportalen.se/Sighting/111062782</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>111065259</v>
+        <v>111062783</v>
       </c>
       <c r="B87" t="n">
         <v>79084</v>
@@ -9726,13 +9812,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>485728</v>
+        <v>485601</v>
       </c>
       <c r="R87" t="n">
-        <v>6917136</v>
+        <v>6916956</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9791,13 +9877,13 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111065259</t>
+          <t>https://artportalen.se/Sighting/111062783</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>111065261</v>
+        <v>111063031</v>
       </c>
       <c r="B88" t="n">
         <v>79084</v>
@@ -9828,17 +9914,17 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485646</v>
+        <v>485601</v>
       </c>
       <c r="R88" t="n">
-        <v>6917010</v>
+        <v>6917014</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9882,12 +9968,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9897,16 +9983,16 @@
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111065261</t>
+          <t>https://artportalen.se/Sighting/111063031</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>111060595</v>
+        <v>111064863</v>
       </c>
       <c r="B89" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9914,37 +10000,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485793</v>
+        <v>485715</v>
       </c>
       <c r="R89" t="n">
-        <v>6917210</v>
+        <v>6917095</v>
       </c>
       <c r="S89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9988,12 +10074,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -10003,16 +10089,16 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060595</t>
+          <t>https://artportalen.se/Sighting/111064863</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>111060596</v>
+        <v>111064864</v>
       </c>
       <c r="B90" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10020,37 +10106,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485774</v>
+        <v>485628</v>
       </c>
       <c r="R90" t="n">
-        <v>6917201</v>
+        <v>6916956</v>
       </c>
       <c r="S90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10094,12 +10180,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10109,16 +10195,16 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060596</t>
+          <t>https://artportalen.se/Sighting/111064864</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>111060597</v>
+        <v>111064865</v>
       </c>
       <c r="B91" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10126,37 +10212,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>485717</v>
+        <v>485894</v>
       </c>
       <c r="R91" t="n">
-        <v>6917113</v>
+        <v>6917512</v>
       </c>
       <c r="S91" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10200,12 +10286,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10215,16 +10301,16 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060597</t>
+          <t>https://artportalen.se/Sighting/111064865</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>111060696</v>
+        <v>111064866</v>
       </c>
       <c r="B92" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10232,37 +10318,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>485595</v>
+        <v>485612</v>
       </c>
       <c r="R92" t="n">
-        <v>6917191</v>
+        <v>6917029</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10306,12 +10392,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Jon Liljebäck, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10321,16 +10407,16 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060696</t>
+          <t>https://artportalen.se/Sighting/111064866</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>111061813</v>
+        <v>111065259</v>
       </c>
       <c r="B93" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10338,37 +10424,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>485794</v>
+        <v>485728</v>
       </c>
       <c r="R93" t="n">
-        <v>6917395</v>
+        <v>6917136</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10412,12 +10498,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10427,16 +10513,16 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061813</t>
+          <t>https://artportalen.se/Sighting/111065259</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>111061814</v>
+        <v>111065261</v>
       </c>
       <c r="B94" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10444,37 +10530,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>485599</v>
+        <v>485646</v>
       </c>
       <c r="R94" t="n">
-        <v>6917223</v>
+        <v>6917010</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10518,12 +10604,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10533,13 +10619,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061814</t>
+          <t>https://artportalen.se/Sighting/111065261</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>111062460</v>
+        <v>111060595</v>
       </c>
       <c r="B95" t="n">
         <v>79946</v>
@@ -10574,13 +10660,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>485779</v>
+        <v>485793</v>
       </c>
       <c r="R95" t="n">
-        <v>6917472</v>
+        <v>6917210</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10624,12 +10710,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10639,13 +10725,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062460</t>
+          <t>https://artportalen.se/Sighting/111060595</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111062461</v>
+        <v>111060596</v>
       </c>
       <c r="B96" t="n">
         <v>79946</v>
@@ -10680,13 +10766,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485633</v>
+        <v>485774</v>
       </c>
       <c r="R96" t="n">
-        <v>6917235</v>
+        <v>6917201</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10730,12 +10816,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10745,13 +10831,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062461</t>
+          <t>https://artportalen.se/Sighting/111060596</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>111062462</v>
+        <v>111060597</v>
       </c>
       <c r="B97" t="n">
         <v>79946</v>
@@ -10786,13 +10872,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>485689</v>
+        <v>485717</v>
       </c>
       <c r="R97" t="n">
-        <v>6917139</v>
+        <v>6917113</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10836,12 +10922,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10851,13 +10937,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062462</t>
+          <t>https://artportalen.se/Sighting/111060597</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>111062463</v>
+        <v>111060696</v>
       </c>
       <c r="B98" t="n">
         <v>79946</v>
@@ -10892,13 +10978,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485683</v>
+        <v>485595</v>
       </c>
       <c r="R98" t="n">
-        <v>6917109</v>
+        <v>6917191</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10942,12 +11028,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10957,13 +11043,13 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062463</t>
+          <t>https://artportalen.se/Sighting/111060696</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>111062464</v>
+        <v>111061813</v>
       </c>
       <c r="B99" t="n">
         <v>79946</v>
@@ -10994,14 +11080,14 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>485607</v>
+        <v>485794</v>
       </c>
       <c r="R99" t="n">
-        <v>6916996</v>
+        <v>6917395</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11048,12 +11134,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11063,13 +11149,13 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062464</t>
+          <t>https://artportalen.se/Sighting/111061813</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>111062465</v>
+        <v>111061814</v>
       </c>
       <c r="B100" t="n">
         <v>79946</v>
@@ -11100,14 +11186,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485602</v>
+        <v>485599</v>
       </c>
       <c r="R100" t="n">
-        <v>6917001</v>
+        <v>6917223</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -11154,12 +11240,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11169,13 +11255,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062465</t>
+          <t>https://artportalen.se/Sighting/111061814</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>111062466</v>
+        <v>111062460</v>
       </c>
       <c r="B101" t="n">
         <v>79946</v>
@@ -11210,10 +11296,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485600</v>
+        <v>485779</v>
       </c>
       <c r="R101" t="n">
-        <v>6916953</v>
+        <v>6917472</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11275,13 +11361,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062466</t>
+          <t>https://artportalen.se/Sighting/111062460</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>111062745</v>
+        <v>111062461</v>
       </c>
       <c r="B102" t="n">
         <v>79946</v>
@@ -11316,10 +11402,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485586</v>
+        <v>485633</v>
       </c>
       <c r="R102" t="n">
-        <v>6917169</v>
+        <v>6917235</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11366,12 +11452,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11381,13 +11467,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062745</t>
+          <t>https://artportalen.se/Sighting/111062461</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>111062746</v>
+        <v>111062462</v>
       </c>
       <c r="B103" t="n">
         <v>79946</v>
@@ -11422,10 +11508,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485619</v>
+        <v>485689</v>
       </c>
       <c r="R103" t="n">
-        <v>6917091</v>
+        <v>6917139</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11472,12 +11558,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11487,13 +11573,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062746</t>
+          <t>https://artportalen.se/Sighting/111062462</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>111062747</v>
+        <v>111062463</v>
       </c>
       <c r="B104" t="n">
         <v>79946</v>
@@ -11528,10 +11614,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485612</v>
+        <v>485683</v>
       </c>
       <c r="R104" t="n">
-        <v>6917070</v>
+        <v>6917109</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11578,12 +11664,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11593,13 +11679,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062747</t>
+          <t>https://artportalen.se/Sighting/111062463</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>111062748</v>
+        <v>111062464</v>
       </c>
       <c r="B105" t="n">
         <v>79946</v>
@@ -11634,10 +11720,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>485603</v>
+        <v>485607</v>
       </c>
       <c r="R105" t="n">
-        <v>6917017</v>
+        <v>6916996</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11684,12 +11770,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11699,13 +11785,13 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062748</t>
+          <t>https://artportalen.se/Sighting/111062464</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>111062749</v>
+        <v>111062465</v>
       </c>
       <c r="B106" t="n">
         <v>79946</v>
@@ -11740,10 +11826,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485581</v>
+        <v>485602</v>
       </c>
       <c r="R106" t="n">
-        <v>6916988</v>
+        <v>6917001</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11790,12 +11876,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11805,13 +11891,13 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062749</t>
+          <t>https://artportalen.se/Sighting/111062465</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>111062750</v>
+        <v>111062466</v>
       </c>
       <c r="B107" t="n">
         <v>79946</v>
@@ -11846,10 +11932,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>485588</v>
+        <v>485600</v>
       </c>
       <c r="R107" t="n">
-        <v>6916984</v>
+        <v>6916953</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11896,12 +11982,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11911,13 +11997,13 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062750</t>
+          <t>https://artportalen.se/Sighting/111062466</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>111062751</v>
+        <v>111062745</v>
       </c>
       <c r="B108" t="n">
         <v>79946</v>
@@ -11952,10 +12038,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485600</v>
+        <v>485586</v>
       </c>
       <c r="R108" t="n">
-        <v>6916950</v>
+        <v>6917169</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12017,13 +12103,13 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062751</t>
+          <t>https://artportalen.se/Sighting/111062745</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>111062754</v>
+        <v>111062746</v>
       </c>
       <c r="B109" t="n">
         <v>79946</v>
@@ -12058,10 +12144,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>485809</v>
+        <v>485619</v>
       </c>
       <c r="R109" t="n">
-        <v>6917422</v>
+        <v>6917091</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12102,7 +12188,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12124,54 +12209,54 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062754</t>
+          <t>https://artportalen.se/Sighting/111062746</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>91845950</v>
+        <v>111062747</v>
       </c>
       <c r="B110" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>485706</v>
+        <v>485612</v>
       </c>
       <c r="R110" t="n">
-        <v>6917375</v>
+        <v>6917070</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12195,12 +12280,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12215,66 +12300,66 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91845950</t>
+          <t>https://artportalen.se/Sighting/111062747</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>111061821</v>
+        <v>111062748</v>
       </c>
       <c r="B111" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485726</v>
+        <v>485603</v>
       </c>
       <c r="R111" t="n">
-        <v>6917354</v>
+        <v>6917017</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12321,12 +12406,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12336,51 +12421,51 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061821</t>
+          <t>https://artportalen.se/Sighting/111062748</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>111061822</v>
+        <v>111062749</v>
       </c>
       <c r="B112" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>485724</v>
+        <v>485581</v>
       </c>
       <c r="R112" t="n">
-        <v>6917367</v>
+        <v>6916988</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12427,12 +12512,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12442,38 +12527,38 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061822</t>
+          <t>https://artportalen.se/Sighting/111062749</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>111062470</v>
+        <v>111062750</v>
       </c>
       <c r="B113" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12483,10 +12568,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485708</v>
+        <v>485588</v>
       </c>
       <c r="R113" t="n">
-        <v>6917366</v>
+        <v>6916984</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12533,12 +12618,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12548,38 +12633,38 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062470</t>
+          <t>https://artportalen.se/Sighting/111062750</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>111062761</v>
+        <v>111062751</v>
       </c>
       <c r="B114" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12589,10 +12674,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>485722</v>
+        <v>485600</v>
       </c>
       <c r="R114" t="n">
-        <v>6917372</v>
+        <v>6916950</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12654,16 +12739,16 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062761</t>
+          <t>https://artportalen.se/Sighting/111062751</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>111062805</v>
+        <v>111062754</v>
       </c>
       <c r="B115" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12671,21 +12756,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12695,10 +12780,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>485617</v>
+        <v>485809</v>
       </c>
       <c r="R115" t="n">
-        <v>6917148</v>
+        <v>6917422</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12739,6 +12824,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12750,7 +12836,7 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12760,62 +12846,54 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062805</t>
+          <t>https://artportalen.se/Sighting/111062754</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>111064861</v>
+        <v>91845950</v>
       </c>
       <c r="B116" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>485708</v>
+        <v>485706</v>
       </c>
       <c r="R116" t="n">
-        <v>6917172</v>
+        <v>6917375</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12839,17 +12917,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>ringhack i tall</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12864,31 +12937,31 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064861</t>
+          <t>https://artportalen.se/Sighting/91845950</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>111061819</v>
+        <v>111061821</v>
       </c>
       <c r="B117" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12896,42 +12969,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>485602</v>
+        <v>485726</v>
       </c>
       <c r="R117" t="n">
-        <v>6917055</v>
+        <v>6917354</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -12993,16 +13058,16 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061819</t>
+          <t>https://artportalen.se/Sighting/111061821</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>111062760</v>
+        <v>111061822</v>
       </c>
       <c r="B118" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13010,42 +13075,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>485628</v>
+        <v>485724</v>
       </c>
       <c r="R118" t="n">
-        <v>6917100</v>
+        <v>6917367</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13092,12 +13149,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13107,16 +13164,16 @@
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062760</t>
+          <t>https://artportalen.se/Sighting/111061822</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>111065258</v>
+        <v>111062470</v>
       </c>
       <c r="B119" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13124,45 +13181,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485643</v>
+        <v>485708</v>
       </c>
       <c r="R119" t="n">
-        <v>6917021</v>
+        <v>6917366</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13206,12 +13255,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13221,38 +13270,38 @@
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111065258</t>
+          <t>https://artportalen.se/Sighting/111062470</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>111062483</v>
+        <v>111062761</v>
       </c>
       <c r="B120" t="n">
-        <v>99118</v>
+        <v>80461</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13262,10 +13311,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485727</v>
+        <v>485722</v>
       </c>
       <c r="R120" t="n">
-        <v>6917357</v>
+        <v>6917372</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13312,12 +13361,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13327,59 +13376,51 @@
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062483</t>
+          <t>https://artportalen.se/Sighting/111062761</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>111062784</v>
+        <v>111062805</v>
       </c>
       <c r="B121" t="n">
-        <v>99118</v>
+        <v>78334</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485733</v>
+        <v>485617</v>
       </c>
       <c r="R121" t="n">
-        <v>6917380</v>
+        <v>6917148</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13420,7 +13461,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13432,7 +13472,7 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13442,51 +13482,59 @@
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062784</t>
+          <t>https://artportalen.se/Sighting/111062805</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>111062785</v>
+        <v>111064861</v>
       </c>
       <c r="B122" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485713</v>
+        <v>485708</v>
       </c>
       <c r="R122" t="n">
-        <v>6917337</v>
+        <v>6917172</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13521,6 +13569,11 @@
           <t>2023-07-25</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>ringhack i tall</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13533,12 +13586,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13548,62 +13601,54 @@
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062785</t>
+          <t>https://artportalen.se/Sighting/111064861</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>111062786</v>
+        <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485720</v>
+        <v>485821</v>
       </c>
       <c r="R123" t="n">
-        <v>6917331</v>
+        <v>6917265</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13627,12 +13672,27 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13641,84 +13701,71 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062786</t>
+          <t>https://artportalen.se/Sighting/137163138</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>111062787</v>
+        <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>99118</v>
+        <v>58008</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485703</v>
+        <v>485720</v>
       </c>
       <c r="R124" t="n">
-        <v>6917324</v>
+        <v>6917309</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13742,12 +13789,27 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13756,73 +13818,76 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck, Jon Liljebäck</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062787</t>
+          <t>https://artportalen.se/Sighting/137163141</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>111064867</v>
+        <v>111061819</v>
       </c>
       <c r="B125" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485712</v>
+        <v>485602</v>
       </c>
       <c r="R125" t="n">
-        <v>6917301</v>
+        <v>6917055</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -13874,7 +13939,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13884,16 +13949,16 @@
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064867</t>
+          <t>https://artportalen.se/Sighting/111061819</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>111062788</v>
+        <v>111062760</v>
       </c>
       <c r="B126" t="n">
-        <v>106244</v>
+        <v>57141</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13901,34 +13966,42 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485721</v>
+        <v>485628</v>
       </c>
       <c r="R126" t="n">
-        <v>6917317</v>
+        <v>6917100</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -13990,16 +14063,16 @@
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062788</t>
+          <t>https://artportalen.se/Sighting/111062760</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>111063032</v>
+        <v>111065258</v>
       </c>
       <c r="B127" t="n">
-        <v>106244</v>
+        <v>57141</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14007,45 +14080,45 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485722</v>
+        <v>485643</v>
       </c>
       <c r="R127" t="n">
-        <v>6917317</v>
+        <v>6917021</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14083,19 +14156,18 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14105,51 +14177,51 @@
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111063032</t>
+          <t>https://artportalen.se/Sighting/111065258</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>111064868</v>
+        <v>111062483</v>
       </c>
       <c r="B128" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485717</v>
+        <v>485727</v>
       </c>
       <c r="R128" t="n">
-        <v>6917305</v>
+        <v>6917357</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14196,12 +14268,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14211,51 +14283,59 @@
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064868</t>
+          <t>https://artportalen.se/Sighting/111062483</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>111062471</v>
+        <v>111062784</v>
       </c>
       <c r="B129" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485717</v>
+        <v>485733</v>
       </c>
       <c r="R129" t="n">
-        <v>6917362</v>
+        <v>6917380</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14296,18 +14376,19 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14317,38 +14398,38 @@
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062471</t>
+          <t>https://artportalen.se/Sighting/111062784</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>111062763</v>
+        <v>111062785</v>
       </c>
       <c r="B130" t="n">
-        <v>99140</v>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14358,10 +14439,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485711</v>
+        <v>485713</v>
       </c>
       <c r="R130" t="n">
-        <v>6917364</v>
+        <v>6917337</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14423,54 +14504,62 @@
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062763</t>
+          <t>https://artportalen.se/Sighting/111062785</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>111060603</v>
+        <v>111062786</v>
       </c>
       <c r="B131" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485831</v>
+        <v>485720</v>
       </c>
       <c r="R131" t="n">
-        <v>6917461</v>
+        <v>6917331</v>
       </c>
       <c r="S131" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14508,18 +14597,19 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14529,54 +14619,62 @@
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060603</t>
+          <t>https://artportalen.se/Sighting/111062786</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>111060606</v>
+        <v>111062787</v>
       </c>
       <c r="B132" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485805</v>
+        <v>485703</v>
       </c>
       <c r="R132" t="n">
-        <v>6917416</v>
+        <v>6917324</v>
       </c>
       <c r="S132" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14614,18 +14712,19 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14635,54 +14734,54 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060606</t>
+          <t>https://artportalen.se/Sighting/111062787</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>111060609</v>
+        <v>111064867</v>
       </c>
       <c r="B133" t="n">
-        <v>79085</v>
+        <v>99118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>485713</v>
+        <v>485712</v>
       </c>
       <c r="R133" t="n">
-        <v>6917226</v>
+        <v>6917301</v>
       </c>
       <c r="S133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14726,12 +14825,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14741,54 +14840,63 @@
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060609</t>
+          <t>https://artportalen.se/Sighting/111064867</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>111060612</v>
+        <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>79085</v>
+        <v>99372</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>485732</v>
+        <v>485715</v>
       </c>
       <c r="R134" t="n">
-        <v>6917237</v>
+        <v>6917314</v>
       </c>
       <c r="S134" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14812,12 +14920,27 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ingen meterhänsyn till bestånd av knärot.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14832,53 +14955,49 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
-        </is>
-      </c>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060612</t>
+          <t>https://artportalen.se/Sighting/137163142</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>111060613</v>
+        <v>111062788</v>
       </c>
       <c r="B135" t="n">
-        <v>79085</v>
+        <v>106244</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14888,13 +15007,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>485790</v>
+        <v>485721</v>
       </c>
       <c r="R135" t="n">
-        <v>6917209</v>
+        <v>6917317</v>
       </c>
       <c r="S135" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14938,12 +15057,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14953,54 +15072,62 @@
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060613</t>
+          <t>https://artportalen.se/Sighting/111062788</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>111060614</v>
+        <v>111063032</v>
       </c>
       <c r="B136" t="n">
-        <v>79085</v>
+        <v>106244</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485602</v>
+        <v>485722</v>
       </c>
       <c r="R136" t="n">
-        <v>6916978</v>
+        <v>6917317</v>
       </c>
       <c r="S136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15038,18 +15165,19 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -15059,54 +15187,54 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060614</t>
+          <t>https://artportalen.se/Sighting/111063032</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>111060698</v>
+        <v>111064868</v>
       </c>
       <c r="B137" t="n">
-        <v>79085</v>
+        <v>106244</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>221144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>485795</v>
+        <v>485717</v>
       </c>
       <c r="R137" t="n">
-        <v>6917340</v>
+        <v>6917305</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15150,12 +15278,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Jon Liljebäck, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -15165,51 +15293,51 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060698</t>
+          <t>https://artportalen.se/Sighting/111064868</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>111061826</v>
+        <v>111062471</v>
       </c>
       <c r="B138" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485809</v>
+        <v>485717</v>
       </c>
       <c r="R138" t="n">
-        <v>6917534</v>
+        <v>6917362</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15256,12 +15384,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -15271,51 +15399,51 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061826</t>
+          <t>https://artportalen.se/Sighting/111062471</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>111061827</v>
+        <v>111062763</v>
       </c>
       <c r="B139" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>485779</v>
+        <v>485711</v>
       </c>
       <c r="R139" t="n">
-        <v>6917362</v>
+        <v>6917364</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15362,12 +15490,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck, Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15377,13 +15505,13 @@
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061827</t>
+          <t>https://artportalen.se/Sighting/111062763</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>111062473</v>
+        <v>111060603</v>
       </c>
       <c r="B140" t="n">
         <v>79085</v>
@@ -15418,13 +15546,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485774</v>
+        <v>485831</v>
       </c>
       <c r="R140" t="n">
-        <v>6917477</v>
+        <v>6917461</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15468,12 +15596,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15483,13 +15611,13 @@
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062473</t>
+          <t>https://artportalen.se/Sighting/111060603</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>111062474</v>
+        <v>111060606</v>
       </c>
       <c r="B141" t="n">
         <v>79085</v>
@@ -15524,13 +15652,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485780</v>
+        <v>485805</v>
       </c>
       <c r="R141" t="n">
-        <v>6917433</v>
+        <v>6917416</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15574,12 +15702,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15589,13 +15717,13 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062474</t>
+          <t>https://artportalen.se/Sighting/111060606</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>111062475</v>
+        <v>111060609</v>
       </c>
       <c r="B142" t="n">
         <v>79085</v>
@@ -15630,13 +15758,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>485772</v>
+        <v>485713</v>
       </c>
       <c r="R142" t="n">
-        <v>6917376</v>
+        <v>6917226</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15680,12 +15808,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15695,13 +15823,13 @@
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062475</t>
+          <t>https://artportalen.se/Sighting/111060609</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>111062476</v>
+        <v>111060612</v>
       </c>
       <c r="B143" t="n">
         <v>79085</v>
@@ -15736,13 +15864,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>485684</v>
+        <v>485732</v>
       </c>
       <c r="R143" t="n">
-        <v>6917119</v>
+        <v>6917237</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15786,12 +15914,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15801,13 +15929,13 @@
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062476</t>
+          <t>https://artportalen.se/Sighting/111060612</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>111062478</v>
+        <v>111060613</v>
       </c>
       <c r="B144" t="n">
         <v>79085</v>
@@ -15842,13 +15970,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>485585</v>
+        <v>485790</v>
       </c>
       <c r="R144" t="n">
-        <v>6916939</v>
+        <v>6917209</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15892,12 +16020,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lovisa Betmark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15907,13 +16035,13 @@
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062478</t>
+          <t>https://artportalen.se/Sighting/111060613</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>111062765</v>
+        <v>111060614</v>
       </c>
       <c r="B145" t="n">
         <v>79085</v>
@@ -15948,13 +16076,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485796</v>
+        <v>485602</v>
       </c>
       <c r="R145" t="n">
-        <v>6917546</v>
+        <v>6916978</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15998,12 +16126,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16013,13 +16141,13 @@
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062765</t>
+          <t>https://artportalen.se/Sighting/111060614</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>111062767</v>
+        <v>111060698</v>
       </c>
       <c r="B146" t="n">
         <v>79085</v>
@@ -16054,13 +16182,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>485804</v>
+        <v>485795</v>
       </c>
       <c r="R146" t="n">
-        <v>6917382</v>
+        <v>6917340</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16104,12 +16232,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Isaac Tiselius</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -16119,13 +16247,13 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062767</t>
+          <t>https://artportalen.se/Sighting/111060698</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>111062768</v>
+        <v>111061826</v>
       </c>
       <c r="B147" t="n">
         <v>79085</v>
@@ -16156,14 +16284,14 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>485622</v>
+        <v>485809</v>
       </c>
       <c r="R147" t="n">
-        <v>6917101</v>
+        <v>6917534</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -16210,12 +16338,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -16225,13 +16353,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062768</t>
+          <t>https://artportalen.se/Sighting/111061826</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>111062769</v>
+        <v>111061827</v>
       </c>
       <c r="B148" t="n">
         <v>79085</v>
@@ -16262,14 +16390,14 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485607</v>
+        <v>485779</v>
       </c>
       <c r="R148" t="n">
-        <v>6917019</v>
+        <v>6917362</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16316,12 +16444,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16331,13 +16459,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062769</t>
+          <t>https://artportalen.se/Sighting/111061827</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>111062770</v>
+        <v>111062473</v>
       </c>
       <c r="B149" t="n">
         <v>79085</v>
@@ -16372,10 +16500,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485597</v>
+        <v>485774</v>
       </c>
       <c r="R149" t="n">
-        <v>6917008</v>
+        <v>6917477</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16422,12 +16550,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -16437,13 +16565,13 @@
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062770</t>
+          <t>https://artportalen.se/Sighting/111062473</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>111062771</v>
+        <v>111062474</v>
       </c>
       <c r="B150" t="n">
         <v>79085</v>
@@ -16478,10 +16606,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>485605</v>
+        <v>485780</v>
       </c>
       <c r="R150" t="n">
-        <v>6916997</v>
+        <v>6917433</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16528,12 +16656,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16543,13 +16671,13 @@
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062771</t>
+          <t>https://artportalen.se/Sighting/111062474</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>111062772</v>
+        <v>111062475</v>
       </c>
       <c r="B151" t="n">
         <v>79085</v>
@@ -16584,10 +16712,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485618</v>
+        <v>485772</v>
       </c>
       <c r="R151" t="n">
-        <v>6916991</v>
+        <v>6917376</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -16634,12 +16762,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -16649,13 +16777,13 @@
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062772</t>
+          <t>https://artportalen.se/Sighting/111062475</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>111062774</v>
+        <v>111062476</v>
       </c>
       <c r="B152" t="n">
         <v>79085</v>
@@ -16690,10 +16818,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>485624</v>
+        <v>485684</v>
       </c>
       <c r="R152" t="n">
-        <v>6916963</v>
+        <v>6917119</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -16740,12 +16868,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16755,13 +16883,13 @@
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062774</t>
+          <t>https://artportalen.se/Sighting/111062476</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>111063029</v>
+        <v>111062478</v>
       </c>
       <c r="B153" t="n">
         <v>79085</v>
@@ -16792,14 +16920,14 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485601</v>
+        <v>485585</v>
       </c>
       <c r="R153" t="n">
-        <v>6917017</v>
+        <v>6916939</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16846,12 +16974,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Lovisa Betmark</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16861,13 +16989,13 @@
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111063029</t>
+          <t>https://artportalen.se/Sighting/111062478</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>111063030</v>
+        <v>111062765</v>
       </c>
       <c r="B154" t="n">
         <v>79085</v>
@@ -16898,14 +17026,14 @@
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485591</v>
+        <v>485796</v>
       </c>
       <c r="R154" t="n">
-        <v>6916938</v>
+        <v>6917546</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16952,12 +17080,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16967,13 +17095,13 @@
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111063030</t>
+          <t>https://artportalen.se/Sighting/111062765</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>111064862</v>
+        <v>111062767</v>
       </c>
       <c r="B155" t="n">
         <v>79085</v>
@@ -17004,14 +17132,14 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>485539</v>
+        <v>485804</v>
       </c>
       <c r="R155" t="n">
-        <v>6916915</v>
+        <v>6917382</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -17058,12 +17186,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Jon Liljebäck, Evalena Sköld</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -17073,16 +17201,16 @@
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111064862</t>
+          <t>https://artportalen.se/Sighting/111062767</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>91845855</v>
+        <v>111062768</v>
       </c>
       <c r="B156" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17090,37 +17218,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485599</v>
+        <v>485622</v>
       </c>
       <c r="R156" t="n">
-        <v>6917016</v>
+        <v>6917101</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17144,12 +17272,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17164,31 +17292,31 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91845855</t>
+          <t>https://artportalen.se/Sighting/111062768</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>111060600</v>
+        <v>111062769</v>
       </c>
       <c r="B157" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17196,21 +17324,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17220,13 +17348,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>485780</v>
+        <v>485607</v>
       </c>
       <c r="R157" t="n">
-        <v>6917204</v>
+        <v>6917019</v>
       </c>
       <c r="S157" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17270,12 +17398,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17285,16 +17413,16 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060600</t>
+          <t>https://artportalen.se/Sighting/111062769</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>111060697</v>
+        <v>111062770</v>
       </c>
       <c r="B158" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17302,21 +17430,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17326,13 +17454,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485822</v>
+        <v>485597</v>
       </c>
       <c r="R158" t="n">
-        <v>6917410</v>
+        <v>6917008</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17376,12 +17504,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Isaac Tiselius</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17391,16 +17519,16 @@
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111060697</t>
+          <t>https://artportalen.se/Sighting/111062770</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>111061817</v>
+        <v>111062771</v>
       </c>
       <c r="B159" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17408,34 +17536,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>485774</v>
+        <v>485605</v>
       </c>
       <c r="R159" t="n">
-        <v>6917379</v>
+        <v>6916997</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -17482,12 +17610,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Jon Liljebäck</t>
+          <t>Hanna Liljebäck</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17497,16 +17625,16 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111061817</t>
+          <t>https://artportalen.se/Sighting/111062771</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>111062755</v>
+        <v>111062772</v>
       </c>
       <c r="B160" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17514,21 +17642,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17538,10 +17666,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>485582</v>
+        <v>485618</v>
       </c>
       <c r="R160" t="n">
-        <v>6917164</v>
+        <v>6916991</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -17603,16 +17731,16 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062755</t>
+          <t>https://artportalen.se/Sighting/111062772</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>111062756</v>
+        <v>111062774</v>
       </c>
       <c r="B161" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17620,21 +17748,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17644,10 +17772,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>485603</v>
+        <v>485624</v>
       </c>
       <c r="R161" t="n">
-        <v>6917017</v>
+        <v>6916963</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -17709,16 +17837,16 @@
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062756</t>
+          <t>https://artportalen.se/Sighting/111062774</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>111062757</v>
+        <v>111063029</v>
       </c>
       <c r="B162" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17726,34 +17854,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>485623</v>
+        <v>485601</v>
       </c>
       <c r="R162" t="n">
-        <v>6916965</v>
+        <v>6917017</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -17800,12 +17928,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Hanna Liljebäck</t>
+          <t>Jon Liljebäck</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17815,16 +17943,16 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111062757</t>
+          <t>https://artportalen.se/Sighting/111063029</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>111063028</v>
+        <v>111063030</v>
       </c>
       <c r="B163" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17832,21 +17960,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17856,10 +17984,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>485601</v>
+        <v>485591</v>
       </c>
       <c r="R163" t="n">
-        <v>6917018</v>
+        <v>6916938</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17920,6 +18048,960 @@
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111063030</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>111064862</v>
+      </c>
+      <c r="B164" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>485539</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6916915</v>
+      </c>
+      <c r="S164" t="n">
+        <v>15</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064862</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>91845855</v>
+      </c>
+      <c r="B165" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>485599</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6917016</v>
+      </c>
+      <c r="S165" t="n">
+        <v>25</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91845855</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>111060600</v>
+      </c>
+      <c r="B166" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>485780</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6917204</v>
+      </c>
+      <c r="S166" t="n">
+        <v>14</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111060600</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>111060697</v>
+      </c>
+      <c r="B167" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>485822</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6917410</v>
+      </c>
+      <c r="S167" t="n">
+        <v>20</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Isaac Tiselius</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111060697</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>111061817</v>
+      </c>
+      <c r="B168" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>485774</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6917379</v>
+      </c>
+      <c r="S168" t="n">
+        <v>15</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111061817</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>111062755</v>
+      </c>
+      <c r="B169" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>485582</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6917164</v>
+      </c>
+      <c r="S169" t="n">
+        <v>15</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Hanna Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Hanna Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111062755</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>111062756</v>
+      </c>
+      <c r="B170" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>485603</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6917017</v>
+      </c>
+      <c r="S170" t="n">
+        <v>15</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Hanna Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Hanna Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111062756</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>111062757</v>
+      </c>
+      <c r="B171" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlig vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>485623</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6916965</v>
+      </c>
+      <c r="S171" t="n">
+        <v>15</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Hanna Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Hanna Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111062757</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>111063028</v>
+      </c>
+      <c r="B172" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Horten, Sultentjärn, höjd öst om sydlik vik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>485601</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6917018</v>
+      </c>
+      <c r="S172" t="n">
+        <v>15</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2023-07-25</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111063028</t>
         </is>
@@ -18089,6 +19171,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 34238-2026 artfynd.xlsx
+++ b/artfynd/A 34238-2026 artfynd.xlsx
@@ -6196,7 +6196,7 @@
         <v>137163134</v>
       </c>
       <c r="B54" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>137163135</v>
       </c>
       <c r="B55" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         <v>137163136</v>
       </c>
       <c r="B56" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137163137</v>
       </c>
       <c r="B57" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>137163139</v>
       </c>
       <c r="B58" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>137163140</v>
       </c>
       <c r="B59" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>137163138</v>
       </c>
       <c r="B123" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>137163141</v>
       </c>
       <c r="B124" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>137163142</v>
       </c>
       <c r="B134" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
